--- a/data/trans_orig/IP24_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP24_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15530</t>
+          <t>16458</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28937</t>
+          <t>29014</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11786</t>
+          <t>12285</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23203</t>
+          <t>23736</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31125</t>
+          <t>30981</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48916</t>
+          <t>49502</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,95%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61298</t>
+          <t>61221</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>74705</t>
+          <t>73777</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>63642</t>
+          <t>63109</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>75059</t>
+          <t>74560</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>128163</t>
+          <t>127577</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>145954</t>
+          <t>146098</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,5%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>94756</t>
+          <t>94289</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>124461</t>
+          <t>123397</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>93660</t>
+          <t>94300</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>121935</t>
+          <t>122350</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>195822</t>
+          <t>195113</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>236276</t>
+          <t>236447</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,52%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>290895</t>
+          <t>291959</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>320600</t>
+          <t>321067</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>354354</t>
+          <t>353939</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>382629</t>
+          <t>381989</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>655369</t>
+          <t>655198</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>695823</t>
+          <t>696532</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>78,12%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33500</t>
+          <t>33165</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50610</t>
+          <t>50880</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34906</t>
+          <t>35560</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52923</t>
+          <t>52508</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71478</t>
+          <t>72573</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>97354</t>
+          <t>97671</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,52%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>122734</t>
+          <t>122464</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>139844</t>
+          <t>140179</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>104565</t>
+          <t>104980</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>122582</t>
+          <t>121928</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,4%</t>
+          <t>66,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>233478</t>
+          <t>233161</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>259354</t>
+          <t>258259</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,06%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>153497</t>
+          <t>154519</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>189808</t>
+          <t>189953</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>151082</t>
+          <t>149294</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>186581</t>
+          <t>186591</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>316124</t>
+          <t>313624</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>366254</t>
+          <t>366695</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,2%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>489127</t>
+          <t>488982</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>525438</t>
+          <t>524416</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>534041</t>
+          <t>534031</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>569540</t>
+          <t>571328</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1033303</t>
+          <t>1032862</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1083433</t>
+          <t>1085933</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,59%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10304</t>
+          <t>10614</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22251</t>
+          <t>22585</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6234</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16391</t>
+          <t>16218</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18894</t>
+          <t>18207</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34608</t>
+          <t>33721</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,29%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>68810</t>
+          <t>68476</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>80757</t>
+          <t>80447</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>67342</t>
+          <t>67515</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>77499</t>
+          <t>77670</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>140186</t>
+          <t>141073</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>155900</t>
+          <t>156587</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,58%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>84538</t>
+          <t>82659</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>112531</t>
+          <t>111240</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65938</t>
+          <t>66771</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>94703</t>
+          <t>92834</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>159176</t>
+          <t>157831</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>198201</t>
+          <t>197125</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,05%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>335333</t>
+          <t>336624</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>363326</t>
+          <t>365205</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>394067</t>
+          <t>395936</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>422832</t>
+          <t>421999</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>738433</t>
+          <t>739509</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>777458</t>
+          <t>778803</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>83,15%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22166</t>
+          <t>22783</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38365</t>
+          <t>39364</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21366</t>
+          <t>21316</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37658</t>
+          <t>37647</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48936</t>
+          <t>48713</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>72426</t>
+          <t>70845</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,05%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>128447</t>
+          <t>127448</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>144646</t>
+          <t>144029</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>132154</t>
+          <t>132165</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>148446</t>
+          <t>148496</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>264199</t>
+          <t>265780</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>287689</t>
+          <t>287912</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,53%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>126335</t>
+          <t>126031</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>161135</t>
+          <t>160032</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>103709</t>
+          <t>102240</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>136198</t>
+          <t>135423</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>237962</t>
+          <t>238331</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>285573</t>
+          <t>288270</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,91%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>544603</t>
+          <t>545706</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>579403</t>
+          <t>579707</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>606117</t>
+          <t>606892</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>638606</t>
+          <t>640075</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1162480</t>
+          <t>1159783</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1210091</t>
+          <t>1209722</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,54%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8087</t>
+          <t>8330</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19128</t>
+          <t>19447</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4204</t>
+          <t>3825</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12607</t>
+          <t>12547</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14174</t>
+          <t>14377</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28564</t>
+          <t>28457</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,36%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40250</t>
+          <t>39931</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51291</t>
+          <t>51048</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55307</t>
+          <t>55367</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>63710</t>
+          <t>64089</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>98729</t>
+          <t>98836</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>113119</t>
+          <t>112916</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,71%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>87098</t>
+          <t>89564</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>117850</t>
+          <t>117629</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59388</t>
+          <t>59781</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>83500</t>
+          <t>87051</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>153776</t>
+          <t>155657</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>192355</t>
+          <t>193825</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,25%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>353083</t>
+          <t>353304</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>383835</t>
+          <t>381369</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>402935</t>
+          <t>399384</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>427047</t>
+          <t>426654</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>765013</t>
+          <t>763543</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>803592</t>
+          <t>801711</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,74%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30719</t>
+          <t>30405</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47925</t>
+          <t>48152</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36354</t>
+          <t>36813</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54934</t>
+          <t>55035</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71684</t>
+          <t>72069</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>98908</t>
+          <t>97788</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,25%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>124778</t>
+          <t>124551</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>141984</t>
+          <t>142298</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>131269</t>
+          <t>131168</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>149849</t>
+          <t>149390</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>259998</t>
+          <t>261118</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>287222</t>
+          <t>286837</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>79,92%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>136754</t>
+          <t>136692</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>171778</t>
+          <t>172716</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>109816</t>
+          <t>108004</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>142331</t>
+          <t>139898</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>255880</t>
+          <t>255509</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>304123</t>
+          <t>302504</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,96%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>531236</t>
+          <t>530298</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>566260</t>
+          <t>566322</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>598222</t>
+          <t>600655</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>630737</t>
+          <t>632549</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1139444</t>
+          <t>1141063</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1187687</t>
+          <t>1188058</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,3%</t>
         </is>
       </c>
     </row>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8863</t>
+          <t>9587</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28794</t>
+          <t>30478</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8391</t>
+          <t>8679</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20393</t>
+          <t>20357</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21582</t>
+          <t>21483</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46197</t>
+          <t>45587</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>39,39%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25884</t>
+          <t>24200</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45815</t>
+          <t>45091</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40674</t>
+          <t>40710</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52676</t>
+          <t>52388</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>69547</t>
+          <t>70157</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>94162</t>
+          <t>94261</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,44%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>86265</t>
+          <t>85871</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>176241</t>
+          <t>176869</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>75042</t>
+          <t>75371</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>121635</t>
+          <t>124536</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>170887</t>
+          <t>169247</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>288500</t>
+          <t>271527</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>27,93%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>281942</t>
+          <t>281314</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>371918</t>
+          <t>372312</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>392412</t>
+          <t>389511</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>439005</t>
+          <t>438676</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>683731</t>
+          <t>700704</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>801344</t>
+          <t>802984</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,59%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18346</t>
+          <t>18460</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33958</t>
+          <t>34545</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21187</t>
+          <t>21715</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39648</t>
+          <t>39336</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43713</t>
+          <t>44611</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67393</t>
+          <t>67025</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>115593</t>
+          <t>115006</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>131205</t>
+          <t>131091</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>142935</t>
+          <t>143247</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>161396</t>
+          <t>160868</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>264741</t>
+          <t>265109</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>288421</t>
+          <t>287523</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,57%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>125294</t>
+          <t>123419</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>237599</t>
+          <t>227771</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>116013</t>
+          <t>115769</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>169253</t>
+          <t>168429</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>252212</t>
+          <t>254374</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>367025</t>
+          <t>366625</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,82%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>424813</t>
+          <t>434641</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>537118</t>
+          <t>538993</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>588444</t>
+          <t>589268</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>641684</t>
+          <t>641928</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1053084</t>
+          <t>1053484</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1167897</t>
+          <t>1165735</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,09%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP24_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP24_R-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>17409</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11285</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>23439</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>20,05%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>12,99%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>26,99%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>22127</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>16458</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>29014</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>15608</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>29612</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>24,52%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>18,24%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>32,15%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>17409</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>12285</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>23736</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>20,05%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30981</t>
+          <t>31572</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49502</t>
+          <t>48512</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,4%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>69436</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>63406</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>75560</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>79,95%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>73,01%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>87,01%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>68108</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>61221</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>73777</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>60623</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>74627</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>75,48%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>67,85%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>81,76%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>69436</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>63109</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>74560</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>79,95%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>67,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>127577</t>
+          <t>128567</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>146098</t>
+          <t>145507</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,17%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90235</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90235</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90235</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>107513</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>92625</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>122391</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>22,57%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>19,45%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>25,7%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>165</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>108323</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>94289</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>123397</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>93853</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>122046</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>26,08%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>22,7%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>29,71%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>107513</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>94300</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>122350</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>22,57%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>195113</t>
+          <t>196107</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>236447</t>
+          <t>236202</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>557</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>368776</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>353898</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>383664</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>77,43%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>74,3%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>80,55%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>462</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>307033</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>291959</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>321067</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>293310</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>321503</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>73,92%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>70,29%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>77,3%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>557</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>368776</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>353939</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>381989</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>77,43%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>77,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>655198</t>
+          <t>655443</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>696532</t>
+          <t>695538</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>78,01%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>718</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>476289</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>476289</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>476289</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>627</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>415356</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>415356</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>415356</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>718</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>476289</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>476289</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>476289</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>43225</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>35277</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>51984</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>27,45%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>22,4%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>33,01%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>41281</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>33165</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>50880</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>32871</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>50977</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>23,81%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>19,13%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>29,35%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>43225</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>35560</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>52508</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>27,45%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>72573</t>
+          <t>71909</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>97671</t>
+          <t>98980</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,92%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>114263</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>105504</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>122211</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>72,55%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>66,99%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>77,6%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>132063</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>122464</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>140179</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>122367</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>140473</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>76,19%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>70,65%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>80,87%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>114263</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>104980</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>121928</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>72,55%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>233161</t>
+          <t>231852</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>258259</t>
+          <t>258923</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>70,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>78,26%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>157488</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>157488</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>157488</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>253</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>173344</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>173344</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>173344</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>157488</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>157488</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>157488</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>168147</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>150318</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>186420</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>23,33%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>20,86%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>25,87%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>260</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>171730</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>154519</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>189953</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>154794</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>190240</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>25,29%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>22,76%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>27,98%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>168147</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>149294</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>186591</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>23,33%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>313624</t>
+          <t>316501</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>366695</t>
+          <t>369737</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,42%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>831</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>552475</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>534202</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>570304</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>76,67%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>74,13%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>79,14%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>755</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>507205</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>488982</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>524416</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>488695</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>524141</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>74,71%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>72,02%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>77,24%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>831</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>552475</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>534031</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>571328</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>76,67%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1032862</t>
+          <t>1029820</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1085933</t>
+          <t>1083056</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>73,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,39%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1083</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>720622</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>720622</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>720622</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1015</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>678935</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>678935</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>678935</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1083</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>720622</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>720622</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>720622</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10376</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6270</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>16313</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>12,39%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7,49%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>19,48%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>15730</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>10614</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>22585</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>10177</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>22650</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>17,27%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11,66%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>24,8%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>10376</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>6063</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>16218</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>12,39%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18207</t>
+          <t>18696</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33721</t>
+          <t>34685</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,84%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>73357</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>67420</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>77463</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>87,61%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>80,52%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>92,51%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>75331</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>68476</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>80447</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>68411</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>80884</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>82,73%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>75,2%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>88,34%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>73357</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>67515</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>77670</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>87,61%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>141073</t>
+          <t>140109</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>156587</t>
+          <t>156098</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,3%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>83733</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>83733</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>83733</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>91061</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>91061</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>91061</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>83733</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>83733</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>83733</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>79312</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>66442</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>93475</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>16,23%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>13,59%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>19,12%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>97610</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>82659</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>111240</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>83656</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>111987</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>21,79%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>18,46%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>24,84%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>79312</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>66771</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>92834</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>16,23%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>157831</t>
+          <t>156578</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>197125</t>
+          <t>195169</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,84%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>409458</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>395295</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>422328</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>83,77%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>80,88%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>86,41%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>505</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>350254</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>336624</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>365205</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>335877</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>364208</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>78,21%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>75,16%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>81,54%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>409458</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>395936</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>421999</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>83,77%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>739509</t>
+          <t>741465</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>778803</t>
+          <t>780056</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,28%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>488770</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>488770</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>488770</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>649</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>447864</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>447864</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>447864</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>488770</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>488770</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>488770</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>28759</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>21198</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>37433</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>16,94%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>12,48%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>22,04%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>30110</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>22783</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>39364</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>22394</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>40038</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>18,05%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13,66%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>23,6%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>28759</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>21316</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>37647</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>16,94%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48713</t>
+          <t>48672</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70845</t>
+          <t>71801</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,33%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>141053</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>132379</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>148614</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>83,06%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>77,96%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>87,52%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>136702</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>127448</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>144029</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>126774</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>144418</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>81,95%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>76,4%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>86,34%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>141053</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>132165</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>148496</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>83,06%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>265780</t>
+          <t>264824</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>287912</t>
+          <t>287953</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,54%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>169812</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>169812</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>169812</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>166812</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>169812</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>169812</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>169812</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>118446</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>102304</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>135212</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>15,96%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>13,78%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>18,21%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>143451</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>126031</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>160032</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>127592</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>161534</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>20,33%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>17,86%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>22,68%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>118446</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>102240</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>135423</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>15,96%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>238331</t>
+          <t>237765</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>288270</t>
+          <t>285685</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,73%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>623869</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>607103</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>640011</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>84,04%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>81,79%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>86,22%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>806</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>562287</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>545706</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>579707</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>544204</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>578146</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>79,67%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>77,32%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>82,14%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>891</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>623869</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>606892</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>640075</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>84,04%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1159783</t>
+          <t>1162368</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1209722</t>
+          <t>1210288</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,58%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1059</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>742315</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>742315</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>742315</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1017</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>705738</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>705738</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>705738</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1059</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>742315</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>742315</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>742315</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7535</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3769</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12324</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5,55%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>18,15%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>12996</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>8330</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>19447</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>8320</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>18962</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>21,89%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>14,03%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>32,75%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>7535</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3825</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>12547</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>11,1%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14377</t>
+          <t>14587</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28457</t>
+          <t>28138</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,11%</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>60379</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>55590</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>88,9%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>81,85%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>94,45%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>46382</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>39931</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>51048</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>40416</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>51058</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>78,11%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>67,25%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>85,97%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>60379</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>55367</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>64089</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>88,9%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>98836</t>
+          <t>99155</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>112916</t>
+          <t>112706</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,54%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>67914</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>67914</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>67914</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>67914</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>67914</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>67914</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>71303</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>60160</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>86275</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>14,66%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>12,37%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>17,74%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>161</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>102538</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>89564</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>117629</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>89327</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>116954</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>21,77%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>19,02%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>24,98%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>71303</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>59781</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>87051</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>14,66%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>155657</t>
+          <t>154693</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>193825</t>
+          <t>193697</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,23%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>587</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>415132</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>400160</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>426275</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>85,34%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>82,26%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>87,63%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>551</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>368395</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>353304</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>381369</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>353979</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>381606</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>78,23%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>75,02%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>80,98%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>587</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>415132</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>399384</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>426654</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>85,34%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>763543</t>
+          <t>763671</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>801711</t>
+          <t>802675</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,84%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>486435</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>486435</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>486435</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>712</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>470933</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>470933</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>470933</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>692</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>486435</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>486435</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>486435</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,107 +4615,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>45566</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>36495</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>55373</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>24,47%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>19,6%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>29,74%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>38833</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>30405</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>48152</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>31167</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>48618</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>22,49%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>17,61%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>27,88%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>45566</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>36813</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>55035</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>24,47%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>18,05%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>28,15%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>84398</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>70941</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>99223</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>23,52%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>19,77%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>29,56%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>84398</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>72069</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>97788</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>23,52%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>20,08%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,65%</t>
         </is>
       </c>
     </row>
@@ -4728,107 +4728,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>140637</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>130830</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>149708</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>75,53%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>70,26%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>80,4%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>200</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>133870</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>124551</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>142298</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>124085</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>141536</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>77,51%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>72,12%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>82,39%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>140637</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>131168</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>149390</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>75,53%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
+          <t>81,95%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>274508</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>259683</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>287965</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>76,48%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>72,35%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>80,23%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>401</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>274508</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>261118</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>286837</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>76,48%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>72,75%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>79,92%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>186203</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>186203</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>186203</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>186203</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>186203</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>186203</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>124404</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>107953</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>140703</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>16,8%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>14,58%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>19,0%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>237</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>154366</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>136692</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>172716</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>137167</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>171263</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>21,96%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>19,44%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>24,57%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>124404</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>108004</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>139898</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>16,8%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>255509</t>
+          <t>254577</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>302504</t>
+          <t>303220</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,0%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>875</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>616149</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>599850</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>632600</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>83,2%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>81,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>85,42%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>822</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>548648</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>530298</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>566322</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>531751</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>565847</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>78,04%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>75,43%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>80,56%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>875</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>616149</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>600655</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>632549</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>83,2%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1141063</t>
+          <t>1140347</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1188058</t>
+          <t>1188990</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>79,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,36%</t>
         </is>
       </c>
     </row>
@@ -5189,52 +5189,52 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>740553</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>740553</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>740553</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1059</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
           <t>703014</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>703014</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>703014</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1059</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>740553</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>740553</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>740553</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11486</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7009</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>16998</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>20,59%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>12,57%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>30,48%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>16888</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9587</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>30478</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>30,89%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>17,53%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>55,74%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>13928</t>
+          <t>9060</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8679</t>
+          <t>5441</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20357</t>
+          <t>14056</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>30816</t>
+          <t>20546</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21483</t>
+          <t>14500</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45587</t>
+          <t>27480</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>26,8%</t>
         </is>
       </c>
     </row>
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>44284</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>38772</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>48761</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>79,41%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>69,52%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>87,43%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>37790</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>24200</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>45091</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>69,11%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>44,26%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>82,47%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>47139</t>
+          <t>37698</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40710</t>
+          <t>32702</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52388</t>
+          <t>41317</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>84928</t>
+          <t>81982</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>70157</t>
+          <t>75048</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>94261</t>
+          <t>88028</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>85,86%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>55770</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>55770</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>55770</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61067</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61067</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61067</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>115744</t>
+          <t>102528</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>115744</t>
+          <t>102528</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>115744</t>
+          <t>102528</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>78081</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>63214</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>103692</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>16,48%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>13,35%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>21,89%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>129</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>112812</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>85871</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>176869</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>24,62%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>18,74%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>38,6%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>91962</t>
+          <t>79352</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>75371</t>
+          <t>67058</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>124536</t>
+          <t>94967</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>204774</t>
+          <t>157433</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>169247</t>
+          <t>138049</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>271527</t>
+          <t>184852</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>20,45%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>395603</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>369992</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>410470</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>83,52%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>78,11%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>86,65%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>510</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>345371</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>281314</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>372312</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>75,38%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>61,4%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>81,26%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>525</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>422085</t>
+          <t>350939</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>389511</t>
+          <t>335324</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>438676</t>
+          <t>363233</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>767457</t>
+          <t>746542</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>700704</t>
+          <t>719123</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>802984</t>
+          <t>765926</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>84,73%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>473684</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>473684</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>473684</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>639</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>458183</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>458183</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>458183</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514047</t>
+          <t>430291</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514047</t>
+          <t>430291</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514047</t>
+          <t>430291</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>972231</t>
+          <t>903975</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>972231</t>
+          <t>903975</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>972231</t>
+          <t>903975</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>25778</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>18378</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>34929</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>15,36%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>10,95%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>20,82%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>25695</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>18460</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>34545</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>17,18%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>12,34%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>23,1%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>29610</t>
+          <t>23674</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21715</t>
+          <t>17446</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39336</t>
+          <t>31945</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>55306</t>
+          <t>49452</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44611</t>
+          <t>40216</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67025</t>
+          <t>61273</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>19,28%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>141997</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>132846</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>149397</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>84,64%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>79,18%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>89,05%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>123856</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>115006</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>131091</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>82,82%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>76,9%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>87,66%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>152973</t>
+          <t>126302</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>143247</t>
+          <t>118031</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>160868</t>
+          <t>132530</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>276828</t>
+          <t>268299</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>265109</t>
+          <t>256478</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>287523</t>
+          <t>277535</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>87,34%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>167775</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>167775</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>167775</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>182583</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>182583</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>182583</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>332134</t>
+          <t>317751</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>332134</t>
+          <t>317751</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>332134</t>
+          <t>317751</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,57 +6561,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>115344</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>98906</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>144738</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>16,54%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>14,19%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>20,76%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>155395</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>123419</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>227771</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>23,46%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>18,63%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>34,39%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>135501</t>
+          <t>112087</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>115769</t>
+          <t>97094</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>168429</t>
+          <t>128435</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>290896</t>
+          <t>227431</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>254374</t>
+          <t>204898</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>366625</t>
+          <t>257387</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>19,44%</t>
         </is>
       </c>
     </row>
@@ -6674,57 +6674,57 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>783</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>581884</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>552490</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>598322</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>83,46%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>79,24%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>85,81%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>753</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>507017</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>434641</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>538993</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>76,54%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>65,61%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>81,37%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>783</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>622196</t>
+          <t>514938</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>589268</t>
+          <t>498590</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>641928</t>
+          <t>529931</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1129213</t>
+          <t>1096823</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1053484</t>
+          <t>1066867</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1165735</t>
+          <t>1119356</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>84,53%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>969</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>938</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>662412</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>662412</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>662412</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>969</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>757697</t>
+          <t>627025</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>757697</t>
+          <t>627025</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>757697</t>
+          <t>627025</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1420109</t>
+          <t>1324254</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1420109</t>
+          <t>1324254</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1420109</t>
+          <t>1324254</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
